--- a/ETL_TESTING_PROJECT_REPORT.XLXS.xlsx
+++ b/ETL_TESTING_PROJECT_REPORT.XLXS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAP-214\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E0A6C9-919C-4BE4-9C28-1140EDAFD2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E757C110-D571-4AC3-AC8D-013417EEC9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2A05D386-A4C4-4CC4-8FC1-E5ED12B4D0EE}"/>
   </bookViews>
